--- a/utility_df.xlsx
+++ b/utility_df.xlsx
@@ -451,16 +451,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FLASH109</t>
+          <t>PUMP101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[&lt;propane: -9.61e+06 kJ/hr, 522 kmol/hr, 127 USD/hr&gt;]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1202.23329690118</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PUMP101</t>
+          <t>DIST114</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[&lt;cooling_water: -4.11e+08 kJ/hr, 2.81e+05 kmol/hr, 137 USD/hr&gt;, &lt;low_pressure_steam: 3.83e+08 kJ/hr, 9.91e+03 kmol/hr, 2.36e+03 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1202.24093268549</v>
+        <v>8.946860348153677</v>
       </c>
     </row>
     <row r="4">
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PUMP112</t>
+          <t>HX117</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[&lt;high_pressure_steam: 6.18e+03 kJ/hr, 0.192 kmol/hr, 0.0609 USD/hr&gt;]</t>
+          <t>[&lt;chilled_water: -5.14e+08 kJ/hr, 3.4e+05 kmol/hr, 2.57e+03 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -505,16 +505,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PUMP108</t>
+          <t>HX110</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[&lt;low_pressure_steam: 2.36e+06 kJ/hr, 61 kmol/hr, 14.5 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.847862251221187e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -523,16 +523,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FLASH118</t>
+          <t>PSA111</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[&lt;low_pressure_steam: 9.44e+06 kJ/hr, 244 kmol/hr, 58.1 USD/hr&gt;]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>737.0790539749057</v>
       </c>
     </row>
     <row r="7">
@@ -541,16 +541,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DIST113</t>
+          <t>PUMP112</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[&lt;cooling_water: -1.21e+07 kJ/hr, 8.26e+03 kmol/hr, 4.03 USD/hr&gt;, &lt;low_pressure_steam: 6.49e+08 kJ/hr, 1.68e+04 kmol/hr, 3.99e+03 USD/hr&gt;]</t>
+          <t>[&lt;high_pressure_steam: 6.18e+03 kJ/hr, 0.192 kmol/hr, 0.0609 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.29838294230985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RCF103-S</t>
+          <t>PUMP108</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.16176663801387</v>
+        <v>1.847862251221187e-12</v>
       </c>
     </row>
     <row r="9">
@@ -577,16 +577,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PSA111</t>
+          <t>HX105</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[&lt;cooling_water: -2.36e+06 kJ/hr, 1.61e+03 kmol/hr, 0.786 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>737.079049795127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -595,12 +595,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RCF106-H</t>
+          <t>HX102</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[&lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;]</t>
+          <t>[&lt;high_pressure_steam: 3.22e+08 kJ/hr, 1e+04 kmol/hr, 3.17e+03 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HX117</t>
+          <t>FLASH118</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[&lt;chilled_water: -5.14e+08 kJ/hr, 3.4e+05 kmol/hr, 2.57e+03 USD/hr&gt;]</t>
+          <t>[&lt;low_pressure_steam: 9.44e+06 kJ/hr, 244 kmol/hr, 58.1 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -631,12 +631,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HX110</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[&lt;low_pressure_steam: 2.36e+06 kJ/hr, 61 kmol/hr, 14.5 USD/hr&gt;]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -649,12 +649,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FLASH107</t>
+          <t>FLASH109</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[&lt;cooling_water: -2.72e+08 kJ/hr, 1.86e+05 kmol/hr, 90.8 USD/hr&gt;]</t>
+          <t>[&lt;propane: -9.61e+06 kJ/hr, 522 kmol/hr, 127 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HX102</t>
+          <t>FLASH107</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[&lt;high_pressure_steam: 3.22e+08 kJ/hr, 1e+04 kmol/hr, 3.17e+03 USD/hr&gt;]</t>
+          <t>[&lt;cooling_water: -2.72e+08 kJ/hr, 1.86e+05 kmol/hr, 90.8 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -685,16 +685,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIST114</t>
+          <t>DIST113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[&lt;cooling_water: -4.11e+08 kJ/hr, 2.81e+05 kmol/hr, 137 USD/hr&gt;, &lt;low_pressure_steam: 3.83e+08 kJ/hr, 9.91e+03 kmol/hr, 2.36e+03 USD/hr&gt;]</t>
+          <t>[&lt;cooling_water: -1.21e+07 kJ/hr, 8.26e+03 kmol/hr, 4.03 USD/hr&gt;, &lt;low_pressure_steam: 6.49e+08 kJ/hr, 1.68e+04 kmol/hr, 3.99e+03 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.946860348251567</v>
+        <v>19.29838294213053</v>
       </c>
     </row>
     <row r="16">
@@ -703,16 +703,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HX105</t>
+          <t>RCF103-S</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[&lt;cooling_water: -2.36e+06 kJ/hr, 1.61e+03 kmol/hr, 0.786 USD/hr&gt;]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>28.16176672756748</v>
       </c>
     </row>
     <row r="17">
@@ -721,12 +721,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>RCF106-H</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[&lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;, &lt;high_pressure_steam: 2.88e+06 kJ/hr, 89.4 kmol/hr, 28.4 USD/hr&gt;]</t>
         </is>
       </c>
       <c r="D17" t="n">
